--- a/AAII_Financials/Yearly/BBAR_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/BBAR_YR_FIN.xlsx
@@ -2081,7 +2081,7 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>1767300</v>
+        <v>1773200</v>
       </c>
       <c r="E41" s="3">
         <v>2634900</v>
@@ -2273,7 +2273,7 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>198500</v>
+        <v>192700</v>
       </c>
       <c r="E45" s="3">
         <v>241400</v>
